--- a/2026/11. 9 Juli 2026/4. JADWAL DAN KALDIK 2026-2027.xlsx
+++ b/2026/11. 9 Juli 2026/4. JADWAL DAN KALDIK 2026-2027.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="389">
   <si>
     <t>JADWAL MATA PELAJARAN DINIYAH MABAIZ   2026/2027</t>
   </si>
@@ -784,22 +784,31 @@
     <t>19 - (1)</t>
   </si>
   <si>
+    <t>10 - 14</t>
+  </si>
+  <si>
+    <t>Ujian Praktek kelas 3</t>
+  </si>
+  <si>
+    <t>Bagi rapot</t>
+  </si>
+  <si>
+    <t>28 - 29</t>
+  </si>
+  <si>
     <t xml:space="preserve">17 - 20 </t>
   </si>
   <si>
     <t>Libur Idul Adha</t>
   </si>
   <si>
-    <t>Bagi rapot</t>
-  </si>
-  <si>
-    <t>28 - 29</t>
+    <t>20 - (12)</t>
   </si>
   <si>
     <t>24 - 29</t>
   </si>
   <si>
-    <t>20 - (12)</t>
+    <t>Ujian Tulis kelas 3</t>
   </si>
   <si>
     <t>KETERANGAN</t>
@@ -5166,13 +5175,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>289890</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>77684</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>289890</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>140803</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5198,7 +5207,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8223885" y="12110085"/>
+          <a:off x="8223885" y="12310110"/>
           <a:ext cx="0" cy="786765"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7709,7 +7718,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AI125"/>
+  <dimension ref="A1:AI126"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" zeroHeight="1"/>
   <cols>
     <col min="1" max="2" width="1.42857142857143" style="323" customWidth="1"/>
@@ -10432,19 +10441,19 @@
       <c r="S51" s="424">
         <v>46516</v>
       </c>
-      <c r="T51" s="354">
+      <c r="T51" s="364">
         <v>46517</v>
       </c>
-      <c r="U51" s="354">
+      <c r="U51" s="364">
         <v>46518</v>
       </c>
-      <c r="V51" s="354">
+      <c r="V51" s="364">
         <v>46519</v>
       </c>
-      <c r="W51" s="354">
+      <c r="W51" s="364">
         <v>46520</v>
       </c>
-      <c r="X51" s="354">
+      <c r="X51" s="364">
         <v>46521</v>
       </c>
       <c r="Y51" s="425">
@@ -10940,11 +10949,11 @@
       <c r="P59" s="385"/>
       <c r="Q59" s="385"/>
       <c r="R59" s="386"/>
-      <c r="S59" s="391">
-        <v>15</v>
+      <c r="S59" s="539" t="s">
+        <v>250</v>
       </c>
       <c r="T59" s="385" t="s">
-        <v>209</v>
+        <v>251</v>
       </c>
       <c r="U59" s="385"/>
       <c r="V59" s="385"/>
@@ -10989,11 +10998,11 @@
       <c r="P60" s="385"/>
       <c r="Q60" s="385"/>
       <c r="R60" s="386"/>
-      <c r="S60" s="384" t="s">
-        <v>250</v>
+      <c r="S60" s="391">
+        <v>15</v>
       </c>
       <c r="T60" s="385" t="s">
-        <v>251</v>
+        <v>209</v>
       </c>
       <c r="U60" s="385"/>
       <c r="V60" s="385"/>
@@ -11038,11 +11047,11 @@
       <c r="P61" s="385"/>
       <c r="Q61" s="385"/>
       <c r="R61" s="386"/>
-      <c r="S61" s="427" t="s">
+      <c r="S61" s="384" t="s">
         <v>254</v>
       </c>
       <c r="T61" s="385" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="U61" s="385"/>
       <c r="V61" s="385"/>
@@ -11051,7 +11060,7 @@
       <c r="Y61" s="385"/>
       <c r="Z61" s="386"/>
       <c r="AA61" s="535" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AB61" s="385" t="s">
         <v>205</v>
@@ -11075,26 +11084,28 @@
       <c r="H62" s="385"/>
       <c r="I62" s="385"/>
       <c r="J62" s="386"/>
-      <c r="K62" s="385">
-        <v>29</v>
-      </c>
-      <c r="L62" s="385" t="s">
-        <v>217</v>
-      </c>
+      <c r="K62" s="389"/>
+      <c r="L62" s="389"/>
       <c r="M62" s="385"/>
       <c r="N62" s="385"/>
       <c r="O62" s="385"/>
       <c r="P62" s="385"/>
       <c r="Q62" s="385"/>
       <c r="R62" s="386"/>
-      <c r="S62" s="385"/>
-      <c r="T62" s="385"/>
+      <c r="S62" s="427" t="s">
+        <v>257</v>
+      </c>
+      <c r="T62" s="385" t="s">
+        <v>238</v>
+      </c>
       <c r="U62" s="385"/>
       <c r="V62" s="385"/>
       <c r="W62" s="385"/>
       <c r="X62" s="385"/>
       <c r="Y62" s="385"/>
       <c r="Z62" s="386"/>
+      <c r="AA62" s="384"/>
+      <c r="AB62" s="385"/>
       <c r="AC62" s="385"/>
       <c r="AD62" s="385"/>
       <c r="AE62" s="385"/>
@@ -11103,91 +11114,97 @@
       <c r="AH62" s="408"/>
       <c r="AI62" s="408"/>
     </row>
-    <row r="63" ht="6.95" customHeight="1" spans="1:35">
-      <c r="C63" s="429"/>
-      <c r="D63" s="429"/>
-      <c r="E63" s="429"/>
-      <c r="F63" s="429"/>
-      <c r="G63" s="429"/>
-      <c r="H63" s="429"/>
-      <c r="I63" s="429"/>
-      <c r="J63" s="429"/>
-      <c r="K63" s="429"/>
-      <c r="L63" s="429"/>
-      <c r="M63" s="429"/>
-      <c r="N63" s="429"/>
-      <c r="O63" s="429"/>
-      <c r="P63" s="429"/>
-      <c r="Q63" s="429"/>
-      <c r="R63" s="429"/>
-      <c r="S63" s="429"/>
-      <c r="T63" s="429"/>
-      <c r="U63" s="429"/>
-      <c r="V63" s="429"/>
-      <c r="W63" s="429"/>
-      <c r="X63" s="429"/>
-      <c r="Y63" s="429"/>
-      <c r="Z63" s="429"/>
-      <c r="AA63" s="429"/>
-      <c r="AB63" s="429"/>
-      <c r="AC63" s="429"/>
-      <c r="AD63" s="429"/>
-      <c r="AE63" s="429"/>
-      <c r="AF63" s="429"/>
-      <c r="AG63" s="429"/>
-    </row>
-    <row r="64" ht="14.25" customHeight="1" spans="1:35">
-      <c r="C64" s="431" t="s">
-        <v>256</v>
-      </c>
-      <c r="D64" s="431"/>
-      <c r="E64" s="431"/>
-      <c r="F64" s="431"/>
-      <c r="G64" s="431"/>
-      <c r="H64" s="431"/>
-      <c r="I64" s="431"/>
-      <c r="J64" s="431"/>
-      <c r="K64" s="431"/>
-      <c r="L64" s="431"/>
-      <c r="M64" s="431"/>
-      <c r="N64" s="431"/>
-      <c r="O64" s="431"/>
-      <c r="P64" s="431"/>
-      <c r="Q64" s="431"/>
-      <c r="S64" s="432"/>
-      <c r="T64" s="432"/>
-      <c r="U64" s="432"/>
-      <c r="V64" s="432"/>
-      <c r="W64" s="432"/>
-      <c r="X64" s="432"/>
-      <c r="Y64" s="432"/>
-      <c r="Z64" s="432"/>
-      <c r="AA64" s="432"/>
-      <c r="AB64" s="432"/>
-      <c r="AC64" s="432"/>
-      <c r="AD64" s="432"/>
-      <c r="AE64" s="432"/>
-      <c r="AF64" s="432"/>
-      <c r="AG64" s="432"/>
+    <row r="63" ht="15.75" spans="1:35">
+      <c r="A63" s="408"/>
+      <c r="B63" s="408"/>
+      <c r="C63" s="385"/>
+      <c r="D63" s="385"/>
+      <c r="E63" s="385"/>
+      <c r="F63" s="385"/>
+      <c r="G63" s="385"/>
+      <c r="H63" s="385"/>
+      <c r="I63" s="385"/>
+      <c r="J63" s="386"/>
+      <c r="K63" s="385">
+        <v>29</v>
+      </c>
+      <c r="L63" s="385" t="s">
+        <v>217</v>
+      </c>
+      <c r="M63" s="385"/>
+      <c r="N63" s="385"/>
+      <c r="O63" s="385"/>
+      <c r="P63" s="385"/>
+      <c r="Q63" s="385"/>
+      <c r="R63" s="386"/>
+      <c r="T63" s="323" t="s">
+        <v>258</v>
+      </c>
+      <c r="U63" s="385"/>
+      <c r="V63" s="385"/>
+      <c r="W63" s="385"/>
+      <c r="X63" s="385"/>
+      <c r="Y63" s="385"/>
+      <c r="Z63" s="386"/>
+      <c r="AC63" s="385"/>
+      <c r="AD63" s="385"/>
+      <c r="AE63" s="385"/>
+      <c r="AF63" s="385"/>
+      <c r="AG63" s="385"/>
+      <c r="AH63" s="408"/>
+      <c r="AI63" s="408"/>
+    </row>
+    <row r="64" ht="6.95" customHeight="1" spans="1:35">
+      <c r="C64" s="429"/>
+      <c r="D64" s="429"/>
+      <c r="E64" s="429"/>
+      <c r="F64" s="429"/>
+      <c r="G64" s="429"/>
+      <c r="H64" s="429"/>
+      <c r="I64" s="429"/>
+      <c r="J64" s="429"/>
+      <c r="K64" s="429"/>
+      <c r="L64" s="429"/>
+      <c r="M64" s="429"/>
+      <c r="N64" s="429"/>
+      <c r="O64" s="429"/>
+      <c r="P64" s="429"/>
+      <c r="Q64" s="429"/>
+      <c r="R64" s="429"/>
+      <c r="S64" s="429"/>
+      <c r="T64" s="429"/>
+      <c r="U64" s="429"/>
+      <c r="V64" s="429"/>
+      <c r="W64" s="429"/>
+      <c r="X64" s="429"/>
+      <c r="Y64" s="429"/>
+      <c r="Z64" s="429"/>
+      <c r="AA64" s="429"/>
+      <c r="AB64" s="429"/>
+      <c r="AC64" s="429"/>
+      <c r="AD64" s="429"/>
+      <c r="AE64" s="429"/>
+      <c r="AF64" s="429"/>
+      <c r="AG64" s="429"/>
     </row>
     <row r="65" ht="14.25" customHeight="1" spans="3:35">
-      <c r="C65" s="433"/>
-      <c r="D65" s="433"/>
-      <c r="E65" s="434" t="s">
-        <v>257</v>
-      </c>
-      <c r="H65" s="434"/>
-      <c r="I65" s="434"/>
-      <c r="J65" s="434"/>
-      <c r="K65" s="434"/>
-      <c r="L65" s="434"/>
-      <c r="M65" s="434"/>
-      <c r="N65" s="434" t="s">
-        <v>258</v>
-      </c>
-      <c r="O65" s="434"/>
-      <c r="P65" s="434"/>
-      <c r="Q65" s="434"/>
+      <c r="C65" s="431" t="s">
+        <v>259</v>
+      </c>
+      <c r="D65" s="431"/>
+      <c r="E65" s="431"/>
+      <c r="F65" s="431"/>
+      <c r="G65" s="431"/>
+      <c r="H65" s="431"/>
+      <c r="I65" s="431"/>
+      <c r="J65" s="431"/>
+      <c r="K65" s="431"/>
+      <c r="L65" s="431"/>
+      <c r="M65" s="431"/>
+      <c r="N65" s="431"/>
+      <c r="O65" s="431"/>
+      <c r="P65" s="431"/>
+      <c r="Q65" s="431"/>
       <c r="S65" s="432"/>
       <c r="T65" s="432"/>
       <c r="U65" s="432"/>
@@ -11205,47 +11222,51 @@
       <c r="AG65" s="432"/>
     </row>
     <row r="66" ht="14.25" customHeight="1" spans="3:35">
-      <c r="C66" s="435"/>
-      <c r="D66" s="435"/>
-      <c r="E66" s="436" t="s">
-        <v>259</v>
-      </c>
-      <c r="H66" s="436"/>
-      <c r="I66" s="436"/>
-      <c r="J66" s="436"/>
-      <c r="K66" s="436"/>
-      <c r="M66" s="436"/>
-      <c r="N66" s="436"/>
+      <c r="C66" s="433"/>
+      <c r="D66" s="433"/>
+      <c r="E66" s="434" t="s">
+        <v>260</v>
+      </c>
+      <c r="H66" s="434"/>
+      <c r="I66" s="434"/>
+      <c r="J66" s="434"/>
+      <c r="K66" s="434"/>
+      <c r="L66" s="434"/>
+      <c r="M66" s="434"/>
+      <c r="N66" s="434" t="s">
+        <v>261</v>
+      </c>
       <c r="O66" s="434"/>
-      <c r="S66" s="437"/>
-      <c r="T66" s="437"/>
-      <c r="U66" s="437"/>
-      <c r="V66" s="437"/>
-      <c r="W66" s="434"/>
-      <c r="X66" s="434"/>
-      <c r="Y66" s="434"/>
-      <c r="Z66" s="434"/>
-      <c r="AA66" s="434"/>
-      <c r="AB66" s="434"/>
-      <c r="AC66" s="434"/>
-      <c r="AD66" s="434"/>
-      <c r="AE66" s="434"/>
-      <c r="AF66" s="434"/>
-      <c r="AG66" s="434"/>
+      <c r="P66" s="434"/>
+      <c r="Q66" s="434"/>
+      <c r="S66" s="432"/>
+      <c r="T66" s="432"/>
+      <c r="U66" s="432"/>
+      <c r="V66" s="432"/>
+      <c r="W66" s="432"/>
+      <c r="X66" s="432"/>
+      <c r="Y66" s="432"/>
+      <c r="Z66" s="432"/>
+      <c r="AA66" s="432"/>
+      <c r="AB66" s="432"/>
+      <c r="AC66" s="432"/>
+      <c r="AD66" s="432"/>
+      <c r="AE66" s="432"/>
+      <c r="AF66" s="432"/>
+      <c r="AG66" s="432"/>
     </row>
     <row r="67" ht="14.25" customHeight="1" spans="3:35">
-      <c r="C67" s="438"/>
-      <c r="D67" s="438"/>
+      <c r="C67" s="435"/>
+      <c r="D67" s="435"/>
       <c r="E67" s="436" t="s">
-        <v>260</v>
-      </c>
-      <c r="H67" s="434"/>
-      <c r="I67" s="434"/>
-      <c r="J67" s="434"/>
-      <c r="K67" s="434"/>
-      <c r="L67" s="434"/>
-      <c r="M67" s="434"/>
-      <c r="N67" s="434"/>
+        <v>262</v>
+      </c>
+      <c r="H67" s="436"/>
+      <c r="I67" s="436"/>
+      <c r="J67" s="436"/>
+      <c r="K67" s="436"/>
+      <c r="M67" s="436"/>
+      <c r="N67" s="436"/>
       <c r="O67" s="434"/>
       <c r="S67" s="437"/>
       <c r="T67" s="437"/>
@@ -11264,10 +11285,10 @@
       <c r="AG67" s="434"/>
     </row>
     <row r="68" ht="14.25" customHeight="1" spans="3:35">
-      <c r="C68" s="439"/>
-      <c r="D68" s="439"/>
-      <c r="E68" s="434" t="s">
-        <v>205</v>
+      <c r="C68" s="438"/>
+      <c r="D68" s="438"/>
+      <c r="E68" s="436" t="s">
+        <v>263</v>
       </c>
       <c r="H68" s="434"/>
       <c r="I68" s="434"/>
@@ -11294,10 +11315,10 @@
       <c r="AG68" s="434"/>
     </row>
     <row r="69" ht="14.25" customHeight="1" spans="3:35">
-      <c r="C69" s="440"/>
-      <c r="D69" s="440"/>
+      <c r="C69" s="439"/>
+      <c r="D69" s="439"/>
       <c r="E69" s="434" t="s">
-        <v>261</v>
+        <v>205</v>
       </c>
       <c r="H69" s="434"/>
       <c r="I69" s="434"/>
@@ -11307,10 +11328,10 @@
       <c r="M69" s="434"/>
       <c r="N69" s="434"/>
       <c r="O69" s="434"/>
-      <c r="S69" s="441"/>
-      <c r="T69" s="441"/>
-      <c r="U69" s="441"/>
-      <c r="V69" s="441"/>
+      <c r="S69" s="437"/>
+      <c r="T69" s="437"/>
+      <c r="U69" s="437"/>
+      <c r="V69" s="437"/>
       <c r="W69" s="434"/>
       <c r="X69" s="434"/>
       <c r="Y69" s="434"/>
@@ -11319,15 +11340,15 @@
       <c r="AB69" s="434"/>
       <c r="AC69" s="434"/>
       <c r="AD69" s="434"/>
-      <c r="AE69" s="432"/>
-      <c r="AF69" s="432"/>
-      <c r="AG69" s="432"/>
+      <c r="AE69" s="434"/>
+      <c r="AF69" s="434"/>
+      <c r="AG69" s="434"/>
     </row>
     <row r="70" ht="14.25" customHeight="1" spans="3:35">
-      <c r="C70" s="442"/>
-      <c r="D70" s="442"/>
+      <c r="C70" s="440"/>
+      <c r="D70" s="440"/>
       <c r="E70" s="434" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H70" s="434"/>
       <c r="I70" s="434"/>
@@ -11337,10 +11358,10 @@
       <c r="M70" s="434"/>
       <c r="N70" s="434"/>
       <c r="O70" s="434"/>
-      <c r="S70" s="437"/>
-      <c r="T70" s="437"/>
-      <c r="U70" s="437"/>
-      <c r="V70" s="437"/>
+      <c r="S70" s="441"/>
+      <c r="T70" s="441"/>
+      <c r="U70" s="441"/>
+      <c r="V70" s="441"/>
       <c r="W70" s="434"/>
       <c r="X70" s="434"/>
       <c r="Y70" s="434"/>
@@ -11349,29 +11370,28 @@
       <c r="AB70" s="434"/>
       <c r="AC70" s="434"/>
       <c r="AD70" s="434"/>
-      <c r="AE70" s="383"/>
-      <c r="AF70" s="383"/>
-      <c r="AG70" s="383"/>
-      <c r="AH70" s="434"/>
-      <c r="AI70" s="434"/>
+      <c r="AE70" s="432"/>
+      <c r="AF70" s="432"/>
+      <c r="AG70" s="432"/>
     </row>
     <row r="71" ht="14.25" customHeight="1" spans="3:35">
-      <c r="C71" s="443"/>
-      <c r="D71" s="444"/>
+      <c r="C71" s="442"/>
+      <c r="D71" s="442"/>
       <c r="E71" s="434" t="s">
-        <v>263</v>
-      </c>
-      <c r="F71" s="434"/>
-      <c r="G71" s="434"/>
+        <v>265</v>
+      </c>
       <c r="H71" s="434"/>
       <c r="I71" s="434"/>
-      <c r="J71" s="437"/>
-      <c r="K71" s="437"/>
+      <c r="J71" s="434"/>
+      <c r="K71" s="434"/>
       <c r="L71" s="434"/>
       <c r="M71" s="434"/>
+      <c r="N71" s="434"/>
+      <c r="O71" s="434"/>
+      <c r="S71" s="437"/>
       <c r="T71" s="437"/>
-      <c r="U71" s="434"/>
-      <c r="V71" s="434"/>
+      <c r="U71" s="437"/>
+      <c r="V71" s="437"/>
       <c r="W71" s="434"/>
       <c r="X71" s="434"/>
       <c r="Y71" s="434"/>
@@ -11380,19 +11400,27 @@
       <c r="AB71" s="434"/>
       <c r="AC71" s="434"/>
       <c r="AD71" s="434"/>
-      <c r="AE71" s="434"/>
+      <c r="AE71" s="383"/>
+      <c r="AF71" s="383"/>
+      <c r="AG71" s="383"/>
+      <c r="AH71" s="434"/>
+      <c r="AI71" s="434"/>
     </row>
     <row r="72" ht="14.25" customHeight="1" spans="3:35">
-      <c r="C72" s="436"/>
+      <c r="C72" s="443"/>
+      <c r="D72" s="444"/>
+      <c r="E72" s="434" t="s">
+        <v>266</v>
+      </c>
       <c r="F72" s="434"/>
       <c r="G72" s="434"/>
       <c r="H72" s="434"/>
-      <c r="I72" s="445"/>
-      <c r="J72" s="446"/>
-      <c r="K72" s="447"/>
-      <c r="L72" s="445"/>
-      <c r="M72" s="445"/>
-      <c r="T72" s="441"/>
+      <c r="I72" s="434"/>
+      <c r="J72" s="437"/>
+      <c r="K72" s="437"/>
+      <c r="L72" s="434"/>
+      <c r="M72" s="434"/>
+      <c r="T72" s="437"/>
       <c r="U72" s="434"/>
       <c r="V72" s="434"/>
       <c r="W72" s="434"/>
@@ -11405,32 +11433,54 @@
       <c r="AD72" s="434"/>
       <c r="AE72" s="434"/>
     </row>
-    <row r="73" ht="14.25" hidden="1" customHeight="1" spans="3:35">
-      <c r="P73" s="448"/>
-      <c r="Q73" s="448"/>
-      <c r="R73" s="448"/>
-      <c r="S73" s="448"/>
-      <c r="T73" s="448"/>
-    </row>
-    <row r="74" customHeight="1"/>
+    <row r="73" ht="14.25" customHeight="1" spans="3:35">
+      <c r="C73" s="436"/>
+      <c r="F73" s="434"/>
+      <c r="G73" s="434"/>
+      <c r="H73" s="434"/>
+      <c r="I73" s="445"/>
+      <c r="J73" s="446"/>
+      <c r="K73" s="447"/>
+      <c r="L73" s="445"/>
+      <c r="M73" s="445"/>
+      <c r="T73" s="441"/>
+      <c r="U73" s="434"/>
+      <c r="V73" s="434"/>
+      <c r="W73" s="434"/>
+      <c r="X73" s="434"/>
+      <c r="Y73" s="434"/>
+      <c r="Z73" s="434"/>
+      <c r="AA73" s="434"/>
+      <c r="AB73" s="434"/>
+      <c r="AC73" s="434"/>
+      <c r="AD73" s="434"/>
+      <c r="AE73" s="434"/>
+    </row>
+    <row r="74" ht="14.25" hidden="1" customHeight="1" spans="3:35">
+      <c r="P74" s="448"/>
+      <c r="Q74" s="448"/>
+      <c r="R74" s="448"/>
+      <c r="S74" s="448"/>
+      <c r="T74" s="448"/>
+    </row>
     <row r="75" customHeight="1"/>
     <row r="76" customHeight="1"/>
     <row r="77" customHeight="1"/>
     <row r="78" customHeight="1"/>
-    <row r="79" customHeight="1" spans="3:35">
-      <c r="N79" s="389" t="s">
-        <v>264</v>
-      </c>
-    </row>
+    <row r="79" customHeight="1"/>
     <row r="80" customHeight="1" spans="3:35">
       <c r="N80" s="389" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="81" customHeight="1"/>
-    <row r="82"/>
+        <v>267</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="14:14">
+      <c r="N81" s="389" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1"/>
     <row r="83"/>
-    <row r="84" customHeight="1"/>
+    <row r="84"/>
     <row r="85" customHeight="1"/>
     <row r="86" customHeight="1"/>
     <row r="87" customHeight="1"/>
@@ -11439,7 +11489,7 @@
     <row r="90" customHeight="1"/>
     <row r="91" customHeight="1"/>
     <row r="92" customHeight="1"/>
-    <row r="93" hidden="1"/>
+    <row r="93" customHeight="1"/>
     <row r="94" hidden="1"/>
     <row r="95" hidden="1"/>
     <row r="96" hidden="1"/>
@@ -11472,6 +11522,7 @@
     <row r="123" hidden="1"/>
     <row r="124" hidden="1"/>
     <row r="125" hidden="1"/>
+    <row r="126" hidden="1"/>
   </sheetData>
   <mergeCells count="52">
     <mergeCell ref="C4:AG4"/>
@@ -11523,9 +11574,9 @@
     <mergeCell ref="AA55:AB55"/>
     <mergeCell ref="AC55:AE55"/>
     <mergeCell ref="AF55:AG55"/>
-    <mergeCell ref="S64:AG64"/>
-    <mergeCell ref="S65:V65"/>
-    <mergeCell ref="W65:AG65"/>
+    <mergeCell ref="S65:AG65"/>
+    <mergeCell ref="S66:V66"/>
+    <mergeCell ref="W66:AG66"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -11546,21 +11597,21 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="313" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B1" s="314"/>
       <c r="C1" s="314"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="313" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B2" s="314"/>
       <c r="C2" s="314"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="314" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B3" s="314"/>
       <c r="C3" s="314"/>
@@ -11572,7 +11623,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="316" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B5" s="317"/>
       <c r="C5" s="315"/>
@@ -11584,21 +11635,21 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="318" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B7" s="318" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C7" s="319" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="319" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B8" s="320" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C8" s="321" t="s">
         <v>98</v>
@@ -11608,62 +11659,62 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="319" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B9" s="321" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C9" s="321" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D9" s="322"/>
       <c r="E9" s="322"/>
     </row>
     <row r="10" ht="90" spans="1:5">
       <c r="A10" s="319" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B10" s="316" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C10" s="321" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D10" s="322"/>
       <c r="E10" s="322"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="319" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B11" s="321" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C11" s="321" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D11" s="322"/>
       <c r="E11" s="322"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="319" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B12" s="321" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C12" s="321" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D12" s="322"/>
       <c r="E12" s="322"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="319" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B13" s="321" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C13" s="321" t="s">
         <v>111</v>
@@ -11673,10 +11724,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="319" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B14" s="321" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C14" s="321" t="s">
         <v>98</v>
@@ -11797,7 +11848,7 @@
   <sheetData>
     <row r="1" ht="34.5" customHeight="1" spans="1:89 16342:16384">
       <c r="A1" s="4" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -11890,7 +11941,7 @@
     </row>
     <row r="3" s="1" customFormat="1" ht="23.1" customHeight="1" spans="1:89 16342:16384">
       <c r="A3" s="5" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -11906,7 +11957,7 @@
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
       <c r="P3" s="7" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q3" s="8"/>
       <c r="R3" s="8"/>
@@ -11922,7 +11973,7 @@
       <c r="AB3" s="8"/>
       <c r="AC3" s="8"/>
       <c r="AE3" s="7" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AF3" s="8"/>
       <c r="AG3" s="8"/>
@@ -11938,7 +11989,7 @@
       <c r="AQ3" s="8"/>
       <c r="AR3" s="8"/>
       <c r="AT3" s="7" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AU3" s="8"/>
       <c r="AV3" s="8"/>
@@ -11954,7 +12005,7 @@
       <c r="BF3" s="8"/>
       <c r="BG3" s="8"/>
       <c r="BI3" s="7" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="BJ3" s="8"/>
       <c r="BK3" s="8"/>
@@ -11970,7 +12021,7 @@
       <c r="BU3" s="8"/>
       <c r="BV3" s="8"/>
       <c r="BX3" s="7" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="BY3" s="8"/>
       <c r="BZ3" s="8"/>
@@ -11988,7 +12039,7 @@
     </row>
     <row r="4" s="2" customFormat="1" ht="18" customHeight="1" spans="1:89 16342:16384">
       <c r="A4" s="9" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="9" t="s">
@@ -12016,7 +12067,7 @@
       </c>
       <c r="N4" s="10"/>
       <c r="P4" s="9" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q4" s="10"/>
       <c r="R4" s="9" t="s">
@@ -12044,7 +12095,7 @@
       </c>
       <c r="AC4" s="10"/>
       <c r="AE4" s="9" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AF4" s="10"/>
       <c r="AG4" s="9" t="s">
@@ -12072,7 +12123,7 @@
       </c>
       <c r="AR4" s="10"/>
       <c r="AT4" s="9" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AU4" s="10"/>
       <c r="AV4" s="9" t="s">
@@ -12100,7 +12151,7 @@
       </c>
       <c r="BG4" s="10"/>
       <c r="BI4" s="9" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="BJ4" s="10"/>
       <c r="BK4" s="9" t="s">
@@ -12128,7 +12179,7 @@
       </c>
       <c r="BV4" s="10"/>
       <c r="BX4" s="9" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="BY4" s="10"/>
       <c r="BZ4" s="9" t="s">
@@ -13364,7 +13415,7 @@
     </row>
     <row r="10" s="1" customFormat="1" ht="26.1" customHeight="1" spans="1:89 16342:16384">
       <c r="A10" s="135" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B10" s="135"/>
       <c r="C10" s="135"/>
@@ -13380,7 +13431,7 @@
       <c r="M10" s="135"/>
       <c r="N10" s="135"/>
       <c r="P10" s="135" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q10" s="135"/>
       <c r="R10" s="135"/>
@@ -13508,7 +13559,7 @@
     </row>
     <row r="11" s="1" customFormat="1" ht="14.1" customHeight="1" spans="1:89 16342:16384">
       <c r="A11" s="146" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B11" s="146"/>
       <c r="C11" s="146"/>
@@ -13517,7 +13568,7 @@
       <c r="F11" s="146"/>
       <c r="G11" s="146"/>
       <c r="P11" s="147" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q11" s="147"/>
       <c r="R11" s="147"/>
@@ -13527,7 +13578,7 @@
       <c r="V11" s="147"/>
       <c r="W11" s="147"/>
       <c r="AE11" s="148" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AF11" s="149"/>
       <c r="AG11" s="149"/>
@@ -13544,7 +13595,7 @@
       <c r="AR11" s="150"/>
       <c r="AS11" s="39"/>
       <c r="AT11" s="148" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="AU11" s="149"/>
       <c r="AV11" s="149"/>
@@ -13560,7 +13611,7 @@
       <c r="BF11" s="149"/>
       <c r="BG11" s="150"/>
       <c r="BI11" s="148" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="BJ11" s="149"/>
       <c r="BK11" s="149"/>
@@ -13576,7 +13627,7 @@
       <c r="BU11" s="149"/>
       <c r="BV11" s="150"/>
       <c r="BX11" s="148" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="BY11" s="149"/>
       <c r="BZ11" s="149"/>
@@ -13597,7 +13648,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -13615,7 +13666,7 @@
         <v>5</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="S12" s="156"/>
       <c r="T12" s="156"/>
@@ -13629,7 +13680,7 @@
       <c r="AB12" s="158"/>
       <c r="AC12" s="158"/>
       <c r="AE12" s="147" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AF12" s="147"/>
       <c r="AG12" s="147"/>
@@ -13640,7 +13691,7 @@
       <c r="AL12" s="147"/>
       <c r="AM12" s="147"/>
       <c r="AT12" s="147" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AU12" s="147"/>
       <c r="AV12" s="147"/>
@@ -13656,7 +13707,7 @@
       <c r="BF12" s="159"/>
       <c r="BG12" s="159"/>
       <c r="BI12" s="147" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="BJ12" s="147"/>
       <c r="BK12" s="147"/>
@@ -13664,7 +13715,7 @@
       <c r="BM12" s="147"/>
       <c r="BN12" s="147"/>
       <c r="BX12" s="160" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="BY12" s="160"/>
       <c r="BZ12" s="160"/>
@@ -13677,7 +13728,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -13695,7 +13746,7 @@
         <v>12</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="U13" s="156"/>
       <c r="V13" s="156"/>
@@ -13747,7 +13798,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="164" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C14" s="165"/>
       <c r="D14" s="165"/>
@@ -13765,7 +13816,7 @@
         <v>20</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="S14" s="156"/>
       <c r="T14" s="156"/>
@@ -13781,7 +13832,7 @@
         <v>1</v>
       </c>
       <c r="AF14" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AJ14" s="2"/>
       <c r="AK14" s="2"/>
@@ -13791,7 +13842,7 @@
         <v>5</v>
       </c>
       <c r="AU14" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AW14" s="15"/>
       <c r="AX14" s="2"/>
@@ -13801,7 +13852,7 @@
         <v>16</v>
       </c>
       <c r="BC14" s="170" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="BD14" s="170"/>
       <c r="BE14" s="170"/>
@@ -13810,21 +13861,21 @@
         <v>7</v>
       </c>
       <c r="BJ14" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="BX14" s="37">
         <v>2</v>
       </c>
       <c r="BY14" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="15.95" customHeight="1" spans="1:89 16342:16384">
       <c r="A15" s="171" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B15" s="172" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C15" s="172"/>
       <c r="D15" s="172"/>
@@ -13834,20 +13885,20 @@
       <c r="H15" s="166"/>
       <c r="I15" s="166"/>
       <c r="P15" s="174" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q15" s="175" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
       <c r="V15" s="2"/>
       <c r="AE15" s="546" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AF15" s="177" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AG15" s="177"/>
       <c r="AH15" s="2"/>
@@ -13859,7 +13910,7 @@
         <v>17</v>
       </c>
       <c r="AU15" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AV15" s="15"/>
       <c r="AW15" s="2"/>
@@ -13871,23 +13922,23 @@
         <v>31</v>
       </c>
       <c r="BC15" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="BD15" s="2"/>
       <c r="BE15" s="170"/>
       <c r="BF15" s="2"/>
       <c r="BI15" s="178" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="BJ15" s="175" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="BK15" s="2"/>
       <c r="BX15" s="547" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="BY15" s="179" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="15.95" customHeight="1" spans="1:89 16342:16384">
@@ -13895,24 +13946,24 @@
         <v>17</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="P16" s="548" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="R16" s="2"/>
       <c r="AE16" s="181">
         <v>17</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AG16" s="2"/>
       <c r="AH16" s="2"/>
@@ -13926,17 +13977,17 @@
       <c r="BE16" s="2"/>
       <c r="BF16" s="2"/>
       <c r="BI16" s="182" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="BJ16" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="BK16" s="2"/>
       <c r="BX16" s="183" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="BY16" s="175" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="15.95" customHeight="1" spans="1:89 16342:16384">
@@ -13958,13 +14009,13 @@
         <v>28</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AE17" s="89">
         <v>22</v>
       </c>
       <c r="AF17" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AG17" s="2"/>
       <c r="AH17" s="2"/>
@@ -13987,7 +14038,7 @@
         <v>27</v>
       </c>
       <c r="BY17" s="190" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="BZ17" s="190"/>
     </row>
@@ -14058,7 +14109,7 @@
     </row>
     <row r="19" s="1" customFormat="1" ht="24" customHeight="1" spans="1:89 16342:16384">
       <c r="A19" s="5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -14074,7 +14125,7 @@
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
       <c r="P19" s="193" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q19" s="194"/>
       <c r="R19" s="194"/>
@@ -14090,7 +14141,7 @@
       <c r="AB19" s="194"/>
       <c r="AC19" s="194"/>
       <c r="AE19" s="7" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AF19" s="8"/>
       <c r="AG19" s="8"/>
@@ -14106,7 +14157,7 @@
       <c r="AQ19" s="8"/>
       <c r="AR19" s="8"/>
       <c r="AT19" s="193" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AU19" s="193"/>
       <c r="AV19" s="193"/>
@@ -14122,7 +14173,7 @@
       <c r="BF19" s="193"/>
       <c r="BG19" s="193"/>
       <c r="BI19" s="5" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="BJ19" s="6"/>
       <c r="BK19" s="6"/>
@@ -14138,7 +14189,7 @@
       <c r="BU19" s="6"/>
       <c r="BV19" s="6"/>
       <c r="BX19" s="5" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="BY19" s="6"/>
       <c r="BZ19" s="6"/>
@@ -14199,7 +14250,7 @@
     </row>
     <row r="20" s="1" customFormat="1" ht="18" customHeight="1" spans="1:89 16342:16384">
       <c r="A20" s="9" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B20" s="10"/>
       <c r="C20" s="9" t="s">
@@ -14227,7 +14278,7 @@
       </c>
       <c r="N20" s="10"/>
       <c r="P20" s="9" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q20" s="10"/>
       <c r="R20" s="9" t="s">
@@ -14255,7 +14306,7 @@
       </c>
       <c r="AC20" s="10"/>
       <c r="AE20" s="9" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AF20" s="10"/>
       <c r="AG20" s="9" t="s">
@@ -14283,7 +14334,7 @@
       </c>
       <c r="AR20" s="10"/>
       <c r="AT20" s="9" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AU20" s="10"/>
       <c r="AV20" s="9" t="s">
@@ -14311,7 +14362,7 @@
       </c>
       <c r="BG20" s="10"/>
       <c r="BI20" s="9" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="BJ20" s="10"/>
       <c r="BK20" s="9" t="s">
@@ -14339,7 +14390,7 @@
       </c>
       <c r="BV20" s="10"/>
       <c r="BX20" s="9" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="BY20" s="10"/>
       <c r="BZ20" s="9" t="s">
@@ -15658,7 +15709,7 @@
       <c r="AQ25" s="18"/>
       <c r="AR25" s="19"/>
       <c r="AT25" s="269" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AU25" s="270"/>
       <c r="AV25" s="270"/>
@@ -15797,7 +15848,7 @@
       <c r="M26" s="28"/>
       <c r="N26" s="278"/>
       <c r="P26" s="279" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q26" s="280"/>
       <c r="R26" s="280"/>
@@ -15814,7 +15865,7 @@
       <c r="AC26" s="280"/>
       <c r="AD26" s="281"/>
       <c r="AE26" s="135" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AF26" s="135"/>
       <c r="AG26" s="135"/>
@@ -15830,7 +15881,7 @@
       <c r="AQ26" s="135"/>
       <c r="AR26" s="135"/>
       <c r="AT26" s="282" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AU26" s="282"/>
       <c r="AV26" s="282"/>
@@ -15839,7 +15890,7 @@
       <c r="AY26" s="282"/>
       <c r="AZ26" s="282"/>
       <c r="BI26" s="283" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="BJ26" s="284"/>
       <c r="BK26" s="284"/>
@@ -15914,7 +15965,7 @@
     </row>
     <row r="27" s="1" customFormat="1" ht="17.1" customHeight="1" spans="1:89 16342:16384">
       <c r="A27" s="287" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B27" s="287"/>
       <c r="C27" s="287"/>
@@ -15930,7 +15981,7 @@
       <c r="M27" s="287"/>
       <c r="N27" s="287"/>
       <c r="AE27" s="147" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AF27" s="147"/>
       <c r="AG27" s="147"/>
@@ -15946,14 +15997,14 @@
       <c r="AQ27" s="288"/>
       <c r="AR27" s="288"/>
       <c r="AT27" s="547" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AU27" s="179" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AV27" s="2"/>
       <c r="BI27" s="289" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="BJ27" s="289"/>
       <c r="BK27" s="289"/>
@@ -15961,7 +16012,7 @@
       <c r="BM27" s="289"/>
       <c r="BN27" s="289"/>
       <c r="BX27" s="135" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="BY27" s="135"/>
       <c r="BZ27" s="135"/>
@@ -16022,7 +16073,7 @@
     </row>
     <row r="28" s="1" customFormat="1" ht="14.1" customHeight="1" spans="1:89 16342:16384">
       <c r="A28" s="147" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B28" s="147"/>
       <c r="C28" s="147"/>
@@ -16031,7 +16082,7 @@
       <c r="F28" s="147"/>
       <c r="G28" s="147"/>
       <c r="P28" s="147" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q28" s="147"/>
       <c r="R28" s="147"/>
@@ -16050,7 +16101,7 @@
         <v>6</v>
       </c>
       <c r="AF28" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AL28" s="2"/>
       <c r="AN28" s="152"/>
@@ -16059,20 +16110,20 @@
       <c r="AQ28" s="152"/>
       <c r="AR28" s="152"/>
       <c r="AT28" s="291" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AU28" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AV28" s="2"/>
       <c r="BI28" s="51">
         <v>4</v>
       </c>
       <c r="BJ28" s="175" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="BX28" s="162" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="BY28" s="162"/>
       <c r="BZ28" s="162"/>
@@ -16147,10 +16198,10 @@
       <c r="AB29" s="290"/>
       <c r="AC29" s="290"/>
       <c r="AE29" s="292" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="AF29" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AG29" s="2"/>
       <c r="AH29" s="2"/>
@@ -16164,23 +16215,23 @@
       <c r="AQ29" s="152"/>
       <c r="AR29" s="152"/>
       <c r="AT29" s="226" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AU29" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AV29" s="2"/>
       <c r="BI29" s="293">
         <v>11</v>
       </c>
       <c r="BJ29" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="BX29" s="549" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="BY29" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="CD29" s="162"/>
       <c r="XDN29" s="3"/>
@@ -16250,10 +16301,10 @@
       <c r="AB30" s="290"/>
       <c r="AC30" s="290"/>
       <c r="AE30" s="295" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AF30" s="296" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG30" s="2"/>
       <c r="AH30" s="2"/>
@@ -16267,23 +16318,23 @@
       <c r="AQ30" s="152"/>
       <c r="AR30" s="152"/>
       <c r="AT30" s="292" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AU30" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AV30" s="2"/>
       <c r="BI30" s="297">
         <v>18</v>
       </c>
       <c r="BJ30" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="BX30" s="298" t="s">
+        <v>370</v>
+      </c>
+      <c r="BY30" s="296" t="s">
         <v>366</v>
-      </c>
-      <c r="BX30" s="298" t="s">
-        <v>367</v>
-      </c>
-      <c r="BY30" s="296" t="s">
-        <v>363</v>
       </c>
       <c r="CD30" s="162"/>
       <c r="XDN30" s="3"/>
@@ -16342,7 +16393,7 @@
         <v>5</v>
       </c>
       <c r="Q31" s="299" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="S31" s="147"/>
       <c r="T31" s="147"/>
@@ -16359,7 +16410,7 @@
         <v>12</v>
       </c>
       <c r="AF31" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AK31" s="2"/>
       <c r="AL31" s="2"/>
@@ -16376,7 +16427,7 @@
         <v>17</v>
       </c>
       <c r="BY31" s="179" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="BZ31" s="3"/>
       <c r="CD31" s="162"/>
@@ -16429,7 +16480,7 @@
         <v>17</v>
       </c>
       <c r="B32" s="301" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
@@ -16447,13 +16498,13 @@
         <v>4</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AE32" s="302">
         <v>15</v>
       </c>
       <c r="AF32" s="179" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AG32" s="15"/>
       <c r="AH32" s="2"/>
@@ -16462,16 +16513,16 @@
       <c r="AK32" s="2"/>
       <c r="AL32" s="2"/>
       <c r="BI32" s="303" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="BJ32" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="BX32" s="550" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="BY32" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="CK32" s="2"/>
       <c r="XDN32" s="3"/>
@@ -16523,7 +16574,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -16538,16 +16589,16 @@
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
       <c r="P33" s="551" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AE33" s="304">
         <v>16</v>
       </c>
       <c r="AF33" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AG33" s="15"/>
       <c r="AH33" s="2"/>
@@ -16559,7 +16610,7 @@
         <v>20</v>
       </c>
       <c r="BY33" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="XDN33" s="3"/>
       <c r="XDO33" s="3"/>
@@ -16620,13 +16671,13 @@
         <v>19</v>
       </c>
       <c r="Q34" s="175" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AE34" s="225">
         <v>20</v>
       </c>
       <c r="AF34" s="296" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AG34" s="2"/>
       <c r="AH34" s="2"/>
@@ -16638,7 +16689,7 @@
         <v>20</v>
       </c>
       <c r="BY34" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="XDN34" s="3"/>
       <c r="XDO34" s="3"/>
@@ -16693,10 +16744,10 @@
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
       <c r="AE35" s="552" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AF35" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AK35" s="2"/>
       <c r="AL35" s="2"/>
